--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N67_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N67_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>53.13088985421365</v>
+        <v>8.633769601309718</v>
       </c>
       <c r="D2" t="n">
-        <v>48.22336407280713</v>
+        <v>7.836296661831159</v>
       </c>
       <c r="E2" t="n">
-        <v>16.4217394685389</v>
+        <v>2.668532663637571</v>
       </c>
       <c r="F2" t="n">
-        <v>18.18043931847493</v>
+        <v>2.954321389252177</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>64.61528470584139</v>
+        <v>10.49998376469923</v>
       </c>
       <c r="D3" t="n">
-        <v>59.51829025415874</v>
+        <v>9.671722166300796</v>
       </c>
       <c r="E3" t="n">
-        <v>16.4217394685389</v>
+        <v>2.668532663637571</v>
       </c>
       <c r="F3" t="n">
-        <v>18.18043931847493</v>
+        <v>2.954321389252177</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>42.25774435262738</v>
+        <v>6.86688345730195</v>
       </c>
       <c r="D4" t="n">
-        <v>37.42343334620165</v>
+        <v>6.081307918757768</v>
       </c>
       <c r="E4" t="n">
-        <v>16.4217394685389</v>
+        <v>2.668532663637571</v>
       </c>
       <c r="F4" t="n">
-        <v>18.18043931847493</v>
+        <v>2.954321389252177</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>44.30647449784871</v>
+        <v>7.199802105900416</v>
       </c>
       <c r="D5" t="n">
-        <v>39.40506085470986</v>
+        <v>6.403322388890352</v>
       </c>
       <c r="E5" t="n">
-        <v>16.4217394685389</v>
+        <v>2.668532663637571</v>
       </c>
       <c r="F5" t="n">
-        <v>18.18043931847493</v>
+        <v>2.954321389252177</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>32.99632275087613</v>
+        <v>5.361902447017371</v>
       </c>
       <c r="D6" t="n">
-        <v>27.83203756987382</v>
+        <v>4.522706105104496</v>
       </c>
       <c r="E6" t="n">
-        <v>16.4217394685389</v>
+        <v>2.668532663637571</v>
       </c>
       <c r="F6" t="n">
-        <v>18.18043931847493</v>
+        <v>2.954321389252177</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>51.64621022598088</v>
+        <v>8.392509161721893</v>
       </c>
       <c r="D7" t="n">
-        <v>54.30104749250933</v>
+        <v>8.823920217532766</v>
       </c>
       <c r="E7" t="n">
-        <v>16.4217394685389</v>
+        <v>2.668532663637571</v>
       </c>
       <c r="F7" t="n">
-        <v>18.18043931847493</v>
+        <v>2.954321389252177</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>11.13824613512231</v>
+        <v>1.809964996957376</v>
       </c>
       <c r="D8" t="n">
-        <v>6.236438899191967</v>
+        <v>1.013421321118695</v>
       </c>
       <c r="E8" t="n">
-        <v>16.4217394685389</v>
+        <v>2.668532663637571</v>
       </c>
       <c r="F8" t="n">
-        <v>18.18043931847493</v>
+        <v>2.954321389252177</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>30.31364220044455</v>
+        <v>4.92596685757224</v>
       </c>
       <c r="D9" t="n">
-        <v>34.91544659803191</v>
+        <v>5.673760072180185</v>
       </c>
       <c r="E9" t="n">
-        <v>16.4217394685389</v>
+        <v>2.668532663637571</v>
       </c>
       <c r="F9" t="n">
-        <v>18.18043931847493</v>
+        <v>2.954321389252177</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>33.7935625231711</v>
+        <v>5.491453910015304</v>
       </c>
       <c r="D10" t="n">
-        <v>18.2794046619669</v>
+        <v>2.970403257569621</v>
       </c>
       <c r="E10" t="n">
-        <v>16.4217394685389</v>
+        <v>2.668532663637571</v>
       </c>
       <c r="F10" t="n">
-        <v>18.18043931847493</v>
+        <v>2.954321389252177</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>27.25750103171917</v>
+        <v>4.429343917654364</v>
       </c>
       <c r="D11" t="n">
-        <v>30.34501475074599</v>
+        <v>4.931064896996223</v>
       </c>
       <c r="E11" t="n">
-        <v>16.4217394685389</v>
+        <v>2.668532663637571</v>
       </c>
       <c r="F11" t="n">
-        <v>18.18043931847493</v>
+        <v>2.954321389252177</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>17.37777551439888</v>
+        <v>2.823888521089819</v>
       </c>
       <c r="D12" t="n">
-        <v>13.92454216247855</v>
+        <v>2.262738101402764</v>
       </c>
       <c r="E12" t="n">
-        <v>16.4217394685389</v>
+        <v>2.668532663637571</v>
       </c>
       <c r="F12" t="n">
-        <v>18.18043931847493</v>
+        <v>2.954321389252177</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>29.142420694624</v>
+        <v>4.7356433628764</v>
       </c>
       <c r="D13" t="n">
-        <v>1.301708279317775</v>
+        <v>0.2115275953891385</v>
       </c>
       <c r="E13" t="n">
-        <v>16.4217394685389</v>
+        <v>2.668532663637571</v>
       </c>
       <c r="F13" t="n">
-        <v>18.18043931847493</v>
+        <v>2.954321389252177</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>20.71058932115176</v>
+        <v>3.365470764687161</v>
       </c>
       <c r="D14" t="n">
-        <v>18.39459461665603</v>
+        <v>2.989121625206606</v>
       </c>
       <c r="E14" t="n">
-        <v>16.4217394685389</v>
+        <v>2.668532663637571</v>
       </c>
       <c r="F14" t="n">
-        <v>18.18043931847493</v>
+        <v>2.954321389252177</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>57.07750107641701</v>
+        <v>9.275093924917766</v>
       </c>
       <c r="D15" t="n">
-        <v>5.461263830188296</v>
+        <v>0.887455372405598</v>
       </c>
       <c r="E15" t="n">
-        <v>16.4217394685389</v>
+        <v>2.668532663637571</v>
       </c>
       <c r="F15" t="n">
-        <v>18.18043931847493</v>
+        <v>2.954321389252177</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>65.69563219327368</v>
+        <v>10.67554023140697</v>
       </c>
       <c r="D16" t="n">
-        <v>4.806421181066631</v>
+        <v>0.7810434419233276</v>
       </c>
       <c r="E16" t="n">
-        <v>16.4217394685389</v>
+        <v>2.668532663637571</v>
       </c>
       <c r="F16" t="n">
-        <v>18.18043931847493</v>
+        <v>2.954321389252177</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
